--- a/AAII_Financials/Quarterly/HSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>HSY</t>
   </si>
@@ -656,539 +656,552 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E7" s="2">
         <v>46110</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45928</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45837</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45746</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45564</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45200</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45109</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45018</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44836</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44745</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44654</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44472</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44381</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44290</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44101</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44010</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43919</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43737</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43191</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43009</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42918</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42827</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2787300</v>
+      </c>
+      <c r="E8" s="3">
         <v>3104200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3091000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3181400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2614700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2805400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2887500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2987500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2074500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3252700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2657100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3030000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2490300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2987600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2652300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2728200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2372600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2666200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2326100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2359800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1989400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2295900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2185200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2219800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1707300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2037300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2068100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2134400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1767200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2016500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1987900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2079600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1751600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1972000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1939600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2033100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1663000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1879700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1970200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2003500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1524000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1881400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1946200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2144100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1818400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1861200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1330500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1753300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1232600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1574100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1534000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1670200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1358200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1604200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1507500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1619700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1372600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1420700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1313300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1298300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1062900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1243000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1223200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1139800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>914800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1170700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1156200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1191100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>892500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1124000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1046300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1211500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>950900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>995700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1103700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1090000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>891400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>970300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1228000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1152600</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1263300</v>
+      </c>
+      <c r="E10" s="3">
         <v>1222700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1144800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1037300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>796300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>944300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1557000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1234200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>841800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1678700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1123100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1359700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1132100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1383400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1144800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1108500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1000000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1245500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1012800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1061500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>926500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1052900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>962000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1080000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>792500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>866600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>911900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>943300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>874700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>892500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>941600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>868100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>800700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>976300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>835900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>943100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>771600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>909400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>742200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>850900</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1231,19 +1244,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>61700</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1251,11 +1265,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>55800</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1263,11 +1277,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>50000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1353,8 +1367,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1475,175 +1492,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E14" s="3">
         <v>13400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>32300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>15100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>25900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>175000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>98800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>39000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>48100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>95100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>37600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>78900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>119600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>43700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>15500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>13900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>87800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>24400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>8300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>9800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>123500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>10700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>10300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>19500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>140400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>10400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>19800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>65900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>15800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>61800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>16400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>41900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>22000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>24700</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>252700</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>14800</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>136100</v>
+      </c>
+      <c r="E15" s="3">
         <v>133000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>132500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>127800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>123800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>119600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>123800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>113300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>110400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>107800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>116700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>103300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>101600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>98200</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1719,8 +1742,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,252 +1786,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2142900</v>
+      </c>
+      <c r="E17" s="3">
         <v>2441600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2636500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2750600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2415100</v>
       </c>
       <c r="H17" s="3">
         <v>2415100</v>
       </c>
       <c r="I17" s="3">
+        <v>2415100</v>
+      </c>
+      <c r="J17" s="3">
         <v>1949000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2329400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1749600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2181100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2207100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2295800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1938900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2191000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2243200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2214800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1930900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1957800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1952000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1806000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1537600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1745800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1876500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1619100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1331400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1665600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1813800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1682400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1365800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1578800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1594000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1676600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1455200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1491900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1647600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1585400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1352800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1682400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1748400</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1650200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>644400</v>
+      </c>
+      <c r="E18" s="3">
         <v>662500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>454500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>430800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>199600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>390300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>938500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>658100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>324800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1071700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>450000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>734200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>551400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>796700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>409100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>513400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>441700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>708400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>374100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>553800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>451800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>550100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>308700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>600700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>375900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>371700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>254300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>452000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>401400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>437700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>393900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>403000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>296400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>480100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>292000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>447700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>310200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>197300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>221800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>353300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2048,618 +2081,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E20" s="3">
         <v>6700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-9400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-10100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-7400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-4800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-22000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-4700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-4900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>1000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>782700</v>
+      </c>
+      <c r="E21" s="3">
         <v>788900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>582400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>561700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>334100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>513700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1062100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>775100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>436700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1181900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>569100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>834100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>656600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>897500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>499700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>603300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>531100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>802000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>456400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>630400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>526100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>629100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>379300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>675700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>444800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>443500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>324500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>517100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>473000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>507700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>453100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>470400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>373400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>555200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>354700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>488000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>372700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>257300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>282800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>437700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>55800</v>
+      </c>
+      <c r="E22" s="3">
         <v>54800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>57700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>59200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>57300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>50600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>41800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>46600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>44300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>41600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>40100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>41800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>40200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>39400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>36700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>36000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>33800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>33500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>30400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>30700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>31700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>37000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>38700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>38100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>38900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>37800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>37400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>35200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>37800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>39400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>39800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>38700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>36800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>31600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>26800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>24900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>24400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>24000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>24200</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>24700</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>588300</v>
+      </c>
+      <c r="E23" s="3">
         <v>592700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>369500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>371900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>149100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>323700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>723100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>518700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>245900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>986300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>319700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>653400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>439500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>759300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>363100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>473100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>403500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>677400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>342900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>521700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>418400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>514200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>263400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>562500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>334100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>335000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>214300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>407400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>363200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>395900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>344000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>356900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>260000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>449200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>260400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>400800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>281100</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>168400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>198600</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>327800</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>130600</v>
+      </c>
+      <c r="E24" s="3">
         <v>157600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>49500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>95600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>86400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>99500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-73500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>72400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>65000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>188800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-29400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>134800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>32500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>172100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-33200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>73600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>87900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>143900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>76700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>117200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>117300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-27900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>115300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>66000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>66200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>9900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>82200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>49900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>92100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>20200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>91400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>36700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>98500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>78900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>126800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>78400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>70100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>81800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>100400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2780,252 +2829,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>457700</v>
+      </c>
+      <c r="E26" s="3">
         <v>435100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>320000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>276300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>62700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>224200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>796600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>446300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>180900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>797500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>349000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>518600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>407000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>587200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>396300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>399500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>315600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>533500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>339800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>444900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>301200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>396900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>291300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>447300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>268000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>268800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>204400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>325200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>313300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>303900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>323800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>265400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>223300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>350700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>181500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>274000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>202700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>98200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>116900</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>457700</v>
+      </c>
+      <c r="E27" s="3">
         <v>435100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>320000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>276300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>62700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>224200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>796600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>446300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>180900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>797500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>349000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>518600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>407000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>587200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>396300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>399500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>315600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>533500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>335600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>444900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>301200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>395800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>291400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>447300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>268900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>271100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>207200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>325300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>312800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>304400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>329000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>263700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>226900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>350200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>181100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>273300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>203500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>125000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>116900</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3146,8 +3204,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3220,8 +3281,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3238,11 +3299,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>7800</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3250,11 +3311,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="3" t="s">
+      <c r="AK29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>0</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3268,8 +3329,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3390,8 +3454,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3512,252 +3579,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>9400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>10100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>7400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>4800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>22000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>4700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>4900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>457700</v>
+      </c>
+      <c r="E33" s="3">
         <v>435100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>320000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>276300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>62700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>224200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>796600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>446300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>180900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>797500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>349000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>518600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>407000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>587200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>396300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>399500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>315600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>533500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>335600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>444900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>301200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>395800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>291400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>447300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>268900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>271100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>207200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>325300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>312800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>304400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>336800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>263700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>226900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>350200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>181100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>273300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>203500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>125000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>116900</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3878,257 +3954,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>457700</v>
+      </c>
+      <c r="E35" s="3">
         <v>435100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>320000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>276300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>62700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>224200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>796600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>446300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>180900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>797500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>349000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>518600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>407000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>587200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>396300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>399500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>315600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>533500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>335600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>444900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>301200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>395800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>291400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>447300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>268900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>271100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>207200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>325300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>312800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>304400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>336800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>263700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>226900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>350200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>181100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>273300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>203500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>125000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>116900</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E38" s="2">
         <v>46110</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45928</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45837</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45746</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45564</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45200</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45109</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45018</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44836</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44745</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44654</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44472</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44381</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44290</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44101</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44010</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43919</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43737</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43191</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43009</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42918</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42827</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4171,8 +4256,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4215,130 +4301,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>791200</v>
+      </c>
+      <c r="E41" s="3">
         <v>877000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>925900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1163000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>912300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1515300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>730700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>615000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>467100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>520400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>401900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>471300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>446200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>460300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>463900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>327700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>339700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>338100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>329300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>675500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>426200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1132200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1144000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1205900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1165300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1094800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>493300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>302600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>366000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>466000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>588000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>823800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>467400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>476400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>380200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>275100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>214100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>235000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>297000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>333300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4459,564 +4549,579 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>907400</v>
+      </c>
+      <c r="E43" s="3">
         <v>974600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>729500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>966400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>820200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>879600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>800400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1142500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>846400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1205700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>823600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1127700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>764300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>856800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>711200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>929500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>654400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>868400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>671500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>841200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>532400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>634800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>615200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>829500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>540400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>705600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>568500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>849200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>538700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>694100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>594100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>814900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>501900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>614300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>588300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>742800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>417500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>595800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>581400</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>759600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1743300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1429100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1429300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1707500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1842300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1467300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1254100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1302000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1459500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1137900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1341000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1347800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1385400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1180400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1173100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1184400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1208200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1031500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>988500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1026500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1060400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>909800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>964200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>958500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>999400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>832200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>815300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>969100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>958000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>791300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>784900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>880700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>916400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>782500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>752800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>938200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>936400</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>795400</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>745700</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>843500</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>364600</v>
+      </c>
+      <c r="E45" s="3">
         <v>324400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>302700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>427200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>714000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>776600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>704400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>377400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>397000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>393700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>118000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>110400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>115100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>116100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>272200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>251100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>226100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>219500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>257000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>198700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>200200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>183200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>254500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>213200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>197800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>222100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>240100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>254100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>230900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>265500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>272200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>274700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>479500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>397300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>280600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>258400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>343600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>247600</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>192800</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3956200</v>
+      </c>
+      <c r="E46" s="3">
         <v>3768500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3588900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4398100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4425600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4804100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3759500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3551800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3335600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3387400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2912100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3190400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2880900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2726100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2620400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2692700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2428500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2457400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2246200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2741900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2219200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2860000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2977900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3207100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2902900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2854800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2117100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2375100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2093600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2216900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2239200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2794000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2365100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2270500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2001900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2214500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1911500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1873900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1816800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2130500</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>174800</v>
+      </c>
+      <c r="E47" s="3">
         <v>179400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>176600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>199600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>204100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>209600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>212900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>207900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>215800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>190400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>207200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>126300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>126100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>145300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>133000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>132200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>139700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>109400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>93100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>77900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>81600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>61000</v>
-      </c>
-      <c r="Y47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>8</v>
@@ -5033,8 +5138,8 @@
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF47" s="3">
         <v>0</v>
@@ -5061,260 +5166,269 @@
         <v>0</v>
       </c>
       <c r="AN47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3">
         <v>1500</v>
-      </c>
-      <c r="AO47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AP47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3777600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3801800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3855000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3763500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3789900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3794100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3796600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3736600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3709500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3640800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3617700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3471600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3337600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3143500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3096200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2950700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2928100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2945000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2937900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2566900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2547900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2518600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2509500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2413100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2388200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2369500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2373800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2325900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2339200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2327200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2130300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2092900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2083800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2119000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2106700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2050100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2033800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2050400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2177200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2159600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5741800</v>
+      </c>
+      <c r="E49" s="3">
         <v>5786500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5823000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4950000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4980800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4921900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4946700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4880300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4910900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4924200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4935500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4945800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4962700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4885500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4893300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4901600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4920300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4930500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4931400</v>
-      </c>
-      <c r="V49" s="3">
-        <v>3891100</v>
       </c>
       <c r="W49" s="3">
         <v>3891100</v>
       </c>
       <c r="X49" s="3">
+        <v>3891100</v>
+      </c>
+      <c r="Y49" s="3">
         <v>3473000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3471100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3460400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3461500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3464500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3481000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3579000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3201000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3204800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3205800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2806400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2806200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2786300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1295100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1297100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1297200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1292300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1305100</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1326400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5435,8 +5549,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5557,130 +5674,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>294800</v>
+      </c>
+      <c r="E52" s="3">
         <v>278200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>270100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>226200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>204300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>199600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>194100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>204500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>202600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>201700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>186100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>163300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>174400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>168300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>206000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>155700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>172300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>202700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>203600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>161400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>144000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>125500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>173300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>174400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>158400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>166700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>168500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>184300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>159800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>108500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>127800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>142800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>150500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>157000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>150000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>93800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>137700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>124300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>225200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>228900</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5801,130 +5924,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13973100</v>
+      </c>
+      <c r="E54" s="3">
         <v>13841300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13741300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13579400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13645700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13967800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12946900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12621400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12415700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12389800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11902900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11935700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11525700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11111500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10948800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10832900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10588900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10645000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10412200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9439200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>8883900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9038100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9131800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9255000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>8911100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8855400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8140400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8464300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7793600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7857400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7703000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7836200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7405700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7332800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5553700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5655500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5380200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>5342400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>5524300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>5845400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5967,8 +6096,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6011,740 +6141,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1303700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1255700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1459700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1450500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1415500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1159200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1214600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1138200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>946000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1086200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1085000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1014100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1004900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>970600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>915300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>876200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>825200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>692300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>671900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>615600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>553600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>580100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>589600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>530000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>531900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>550800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>553600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>479800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>500600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>502300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>581500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>496900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>520000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>523200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>529400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>471500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>499100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>522500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>458000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>976500</v>
+      </c>
+      <c r="E58" s="3">
         <v>723200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>771500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>763600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>514500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>793900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1952600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2140700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1964700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1630300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1059400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>862000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>901700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1394000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1447400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1546100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1667500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>876100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>942300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>413200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>211000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>418400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>512900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>834000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>986700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1626300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>735700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1628400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1240000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1172300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1203300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1452300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1351300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2549500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>859500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1115700</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>622100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>487600</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>632700</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>862400</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E59" s="3">
         <v>136400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>63700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>98500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>98800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>51000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>71800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>37200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>75500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>29500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>54900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>135100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>839200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>927200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>757200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>864300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>858700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>821500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>760300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>802600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>798800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>804600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>698000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>734600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>722300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>800400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>667700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>725200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>712900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>725000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>666100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>636000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>693900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>692500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>648600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>724100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>754200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>696600</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3352500</v>
+      </c>
+      <c r="E60" s="3">
         <v>3039800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3011900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3227800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2893300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3016100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3929500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4195000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3885600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3489000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3008400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2936500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2726100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3281300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3257200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3388600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3300900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2565600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2493300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1906500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1587000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1774600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1891700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2228200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2214800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2892800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2008800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2982400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2387400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2398200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2418600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2758800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2514300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3705500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2076500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2337700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1742200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1710900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1909400</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2017000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4946800</v>
+      </c>
+      <c r="E61" s="3">
         <v>4957900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4967100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4976800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5486300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5496900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3495000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3503500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3797300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4066400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4066200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4370100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4376900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3630700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3344000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3340700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3340500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4088400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4086600</v>
-      </c>
-      <c r="V61" s="3">
-        <v>4095200</v>
       </c>
       <c r="W61" s="3">
         <v>4095200</v>
       </c>
       <c r="X61" s="3">
+        <v>4095200</v>
+      </c>
+      <c r="Y61" s="3">
         <v>4094200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4089800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4093200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4091200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3453500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3530800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2892300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2888000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3236300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3254300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3253900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3249700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2059900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2061000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2054100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2349800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2350900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2347500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2362500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>257300</v>
+      </c>
+      <c r="E62" s="3">
         <v>269800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>304900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>225600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>227600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>241700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>262600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>278600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>273500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>267700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>263900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>252300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>256300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>253300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1048100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1020500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1055800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1075400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1075100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>900400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>927800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>904500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>912500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>864900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>849000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>834600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>855800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>828000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>834000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>799500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>622900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>574200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>577900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>577700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>484600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>424700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>418300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>435100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>439700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>523800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6865,8 +7014,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6987,8 +7139,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7109,130 +7264,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9410400</v>
+      </c>
+      <c r="E66" s="3">
         <v>9107400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9104500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9015000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9131100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9282900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8232200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8416400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8405800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8281500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7803900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7968000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7830900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7653200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7649300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7749800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7697100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7729500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7655000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6910900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6618800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6782100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6897500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7189200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7157500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7184200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6401200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6711100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6118400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6442600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6304300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6601300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6355700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6360700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4638400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4832200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4524900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4512300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>4738500</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>4950000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7275,8 +7436,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7397,8 +7559,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7519,8 +7684,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7641,8 +7809,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7763,130 +7934,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5814200</v>
+      </c>
+      <c r="E72" s="3">
         <v>5643400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5495400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5447400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5442900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5652100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5698300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5172700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4997300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5087100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4562300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4451500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4171000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3970600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3589800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3401200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3208600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3071400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2719900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2565500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2301800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2162500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1928700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1800200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1516500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1404500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1290500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>7525700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>7358300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>7193200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>7032000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6843100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6727100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6634300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6371100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>6325000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>6187400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>6112500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>6116000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>6129100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8007,8 +8184,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8129,8 +8309,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8251,130 +8434,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4562700</v>
+      </c>
+      <c r="E76" s="3">
         <v>4733800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4636800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4564400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4514600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4684900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4714700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4205000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4009900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4108300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4099100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3967600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3694800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3458400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3299500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3083100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2891700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2915500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2757200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2528300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2265000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2256000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2234400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2065900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1753600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1671200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1739200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1753200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1675100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1414700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1398700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1234900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1049900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>972100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>915300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>823300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>855300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>830100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>785900</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>895400</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8495,257 +8684,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E80" s="2">
         <v>46110</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45928</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45837</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45746</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45564</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45200</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45109</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45018</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44836</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44745</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44654</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44472</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44381</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44290</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44101</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44010</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43919</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43737</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43191</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43009</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42918</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42827</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>457700</v>
+      </c>
+      <c r="E81" s="3">
         <v>435100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>320000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>276300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>62700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>224200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>796600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>446300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>180900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>797500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>349000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>518600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>407000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>587200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>396300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>399500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>315600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>533500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>335600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>444900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>301200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>395800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>291400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>447300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>268900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>271100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>207200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>325300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>312800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>304400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>336800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>263700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>226900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>350200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>181100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>273300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>203500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>125000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>116900</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8788,130 +8986,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>102600</v>
+      </c>
+      <c r="E83" s="3">
         <v>99000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>97800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>93700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>90900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>88200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>87600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>83400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>81000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>79000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>80000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>74300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>73800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>71200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>99900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>94200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>93800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>91000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>83000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>78000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>76000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>77900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>77200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>75200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>71900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>70600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>72700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>74500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>72000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>72300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>69300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>74800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>76600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>74400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>67500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>62200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>67100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>65000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>59900</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9032,8 +9234,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9154,8 +9359,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9276,8 +9484,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9398,8 +9609,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9520,130 +9734,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>419300</v>
+      </c>
+      <c r="E89" s="3">
         <v>468800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>926600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>841900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>112200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>396700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>941600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>695300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>325600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>569100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>757600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>515700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>294400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>755400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>767600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>446400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>457300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>656500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>679200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>386100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>408000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>621100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>603600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>481200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>368100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>235200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>770500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>314100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>349400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>330000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>707100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>290000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>250800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>352100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>623600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>290200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>101300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>234500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>562700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9686,130 +9906,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-89800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-114600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-138100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-85900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-85100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-145500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-134500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-128000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-130200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-213300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-222500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-218100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-154400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-176100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-159500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-119000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-99900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-141100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-148400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-119800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-113100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-114500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-149600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-106300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-86600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-99200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-81600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-60300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-83500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-92800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-87400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-105300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-75800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-60100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-108800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-64200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-51400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-33300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-202500</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-232300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9930,8 +10154,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10052,130 +10279,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-117100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-896500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-80400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-154800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-147000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-411000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-159600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-162200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-227600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-463100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-219500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-327700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-188300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-277400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-159000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-187000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-164000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1383100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-139600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-563100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-137000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-190000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-131500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-99100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-110700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-82800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-491300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-94800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-111600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-530700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>92000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-82500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-981800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-141500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-80900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-65600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-40700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-109500</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-81400</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10218,130 +10451,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>286400</v>
+      </c>
+      <c r="E96" s="3">
         <v>288000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>271300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>271100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>271200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>271600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>270500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>270400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>270500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>273400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>237800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>237700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>206200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>207400</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-207000</v>
       </c>
       <c r="R96" s="3">
         <v>-207000</v>
       </c>
       <c r="S96" s="3">
+        <v>-207000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-179900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-181100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-180800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-180900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-161600</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-162700</v>
       </c>
       <c r="Y96" s="3">
         <v>-162700</v>
       </c>
       <c r="Z96" s="3">
+        <v>-162700</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-163700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-156500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-157800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-157100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-157700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-149000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-146500</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-147300</v>
       </c>
       <c r="AH96" s="3">
         <v>-147300</v>
       </c>
       <c r="AI96" s="3">
+        <v>-147300</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-133600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-134300</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-134400</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-135700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-128100</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-128000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-127800</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-128600</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10462,8 +10699,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10584,8 +10824,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10706,370 +10949,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-425200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-402800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-266900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-514000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-559600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>537100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-449500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-394100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-231200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-221700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-363900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-277700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>45600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-552200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-339700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-320600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-292000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-463500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>356700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-549800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-491900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-479300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-315800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-199800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>495600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-498600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>115900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-357600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-341100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-412900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-24100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-172700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>725900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-378000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-150600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-58300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-256900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-484200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>90400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-2300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>34700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>14400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1400</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>6600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-26500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-18400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-14400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>21200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>23300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-20300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-14400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>21200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>23300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-20300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>3700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>6600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-18700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-4600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>2300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>1600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-85800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-48900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-237200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>250700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-602900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>784500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>115800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>147900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-53300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>118500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-69400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>25100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-14200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>136100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-346300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>249300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-706000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-11700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-61900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>40600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>70500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>601500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>190600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-63300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-100000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-122000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-235800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>356400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-9100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>96300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>105100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>61000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-21000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-61900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-36400</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>83100</v>
       </c>
     </row>
